--- a/config/auto_configs/2019_Hyundai_Hyundai_Nexo(FE)_113kW.xlsx
+++ b/config/auto_configs/2019_Hyundai_Hyundai_Nexo(FE)_113kW.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,6 +1023,182 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>IBU-TPMS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HMA_003C9</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HMA_00377</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AFC-D</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HMA_0041A</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AFC-P</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HMA_0041E</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AFC-RL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HMA_00416</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AFC-RR</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HMA_00427</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AHS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HMA_003C1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HMA_002C2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
